--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -203,7 +203,7 @@
     <t>Último día de trabajo</t>
   </si>
   <si>
-    <t>Años completos</t>
+    <t>Antigüedad: años completos</t>
   </si>
   <si>
     <t>Última remuneración mensual</t>
@@ -212,7 +212,7 @@
     <t>Sueldo más lo fijo que recibes cada mes (colación, movilización, cotizaciones). Sin horas extra ni gratificación anual.</t>
   </si>
   <si>
-    <t>Última anualidad</t>
+    <t>Antigüedad: último aniversario</t>
   </si>
   <si>
     <t>Motivo del término</t>
@@ -221,7 +221,7 @@
     <t>Necesidades de la empresa (despido art. 161)</t>
   </si>
   <si>
-    <t>Meses desde la última anualidad</t>
+    <t>Antigüedad: meses</t>
   </si>
   <si>
     <t>Te avisaron con 30 días o más de anticipación</t>
@@ -230,7 +230,7 @@
     <t>No</t>
   </si>
   <si>
-    <t>Días sueltos</t>
+    <t>Antigüedad: días</t>
   </si>
   <si>
     <t>Días hábiles de vacaciones de años anteriores sin tomar</t>

--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -1473,7 +1473,7 @@
       <formula2>1000000000000</formula2>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B7">
-      <formula1>"AFP Capital,AFP Cuprum,AFP Habitat,AFP Modelo,AFP PlanVital,AFP ProVida,AFP Uno"</formula1>
+      <formula1>'Tablas oficiales'!$B$4:$B$10</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B8">
       <formula1>"Fonasa,Isapre"</formula1>

--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito»: pones tus fechas, tu remuneración y el motivo del término, y te dice las indemnizaciones y las vacaciones pendientes y proporcionales.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 8/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -302,7 +302,7 @@
     <t>Tablas oficiales de Chile</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 8/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -362,13 +362,13 @@
     <t>Unidad de Fomento (UF)</t>
   </si>
   <si>
-    <t>Valor al 8/10/2026</t>
+    <t>Valor al 9/10/2026</t>
   </si>
   <si>
     <t>CLP</t>
   </si>
   <si>
-    <t>8/10/2026</t>
+    <t>9/10/2026</t>
   </si>
   <si>
     <t>https://www.sii.cl/valores_y_fechas/uf/uf2026.htm</t>
@@ -1690,7 +1690,7 @@
         <v>61</v>
       </c>
       <c r="B6" s="22">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>62</v>
@@ -2196,7 +2196,7 @@
         <v>115</v>
       </c>
       <c r="C11" s="35">
-        <v>41122.74</v>
+        <v>41130.94</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>116</v>

--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito»: pones tus fechas, tu remuneración y el motivo del término, y te dice las indemnizaciones y las vacaciones pendientes y proporcionales.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 13/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -302,7 +302,7 @@
     <t>Tablas oficiales de Chile</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 13/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1690,7 +1690,7 @@
         <v>61</v>
       </c>
       <c r="B6" s="22">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>62</v>

--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -362,13 +362,13 @@
     <t>Unidad de Fomento (UF)</t>
   </si>
   <si>
-    <t>Valor al 9/10/2026</t>
+    <t>Valor al 13/10/2026</t>
   </si>
   <si>
     <t>CLP</t>
   </si>
   <si>
-    <t>9/10/2026</t>
+    <t>13/10/2026</t>
   </si>
   <si>
     <t>https://www.sii.cl/valores_y_fechas/uf/uf2026.htm</t>
@@ -2196,7 +2196,7 @@
         <v>115</v>
       </c>
       <c r="C11" s="35">
-        <v>41130.94</v>
+        <v>41152.13</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>116</v>

--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito»: pones tus fechas, tu remuneración y el motivo del término, y te dice las indemnizaciones y las vacaciones pendientes y proporcionales.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -302,7 +302,7 @@
     <t>Tablas oficiales de Chile</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1690,7 +1690,7 @@
         <v>61</v>
       </c>
       <c r="B6" s="22">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>62</v>

--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito»: pones tus fechas, tu remuneración y el motivo del término, y te dice las indemnizaciones y las vacaciones pendientes y proporcionales.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -302,7 +302,7 @@
     <t>Tablas oficiales de Chile</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1690,7 +1690,7 @@
         <v>61</v>
       </c>
       <c r="B6" s="22">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>62</v>

--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito»: pones tus fechas, tu remuneración y el motivo del término, y te dice las indemnizaciones y las vacaciones pendientes y proporcionales.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -302,7 +302,7 @@
     <t>Tablas oficiales de Chile</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -362,13 +362,13 @@
     <t>Unidad de Fomento (UF)</t>
   </si>
   <si>
-    <t>Valor al 9/10/2026</t>
+    <t>Valor al 16/10/2026</t>
   </si>
   <si>
     <t>CLP</t>
   </si>
   <si>
-    <t>9/10/2026</t>
+    <t>16/10/2026</t>
   </si>
   <si>
     <t>https://www.sii.cl/valores_y_fechas/uf/uf2026.htm</t>
@@ -1690,7 +1690,7 @@
         <v>61</v>
       </c>
       <c r="B6" s="22">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>62</v>
@@ -2196,7 +2196,7 @@
         <v>115</v>
       </c>
       <c r="C11" s="35">
-        <v>41130.94</v>
+        <v>41168.03</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>116</v>

--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito»: pones tus fechas, tu remuneración y el motivo del término, y te dice las indemnizaciones y las vacaciones pendientes y proporcionales.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -302,7 +302,7 @@
     <t>Tablas oficiales de Chile</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -362,13 +362,13 @@
     <t>Unidad de Fomento (UF)</t>
   </si>
   <si>
-    <t>Valor al 16/10/2026</t>
+    <t>Valor al 19/10/2026</t>
   </si>
   <si>
     <t>CLP</t>
   </si>
   <si>
-    <t>16/10/2026</t>
+    <t>19/10/2026</t>
   </si>
   <si>
     <t>https://www.sii.cl/valores_y_fechas/uf/uf2026.htm</t>
@@ -1690,7 +1690,7 @@
         <v>61</v>
       </c>
       <c r="B6" s="22">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>62</v>
@@ -2196,7 +2196,7 @@
         <v>115</v>
       </c>
       <c r="C11" s="35">
-        <v>41168.03</v>
+        <v>41183.94</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>116</v>

--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="154">
   <si>
     <t>Planilla de sueldo y finiquito Chile 2026</t>
   </si>
@@ -32,7 +32,7 @@
     <t>«Finiquito»: pones tus fechas, tu remuneración y el motivo del término, y te dice las indemnizaciones y las vacaciones pendientes y proporcionales.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -50,12 +50,24 @@
     <t>Sueldo líquido: AFP, salud, seguro de cesantía e impuesto único</t>
   </si>
   <si>
+    <t>AFP Capital</t>
+  </si>
+  <si>
+    <t>AFP Cuprum</t>
+  </si>
+  <si>
     <t>Paso a paso</t>
   </si>
   <si>
+    <t>AFP Habitat</t>
+  </si>
+  <si>
     <t>TUS DATOS</t>
   </si>
   <si>
+    <t>AFP Modelo</t>
+  </si>
+  <si>
     <t>Sueldo bruto imponible</t>
   </si>
   <si>
@@ -65,6 +77,9 @@
     <t>Cotizaciones</t>
   </si>
   <si>
+    <t>AFP PlanVital</t>
+  </si>
+  <si>
     <t>Colación y movilización</t>
   </si>
   <si>
@@ -74,15 +89,18 @@
     <t>Tope imponible del mes</t>
   </si>
   <si>
+    <t>AFP ProVida</t>
+  </si>
+  <si>
     <t>Tu AFP</t>
   </si>
   <si>
-    <t>AFP Habitat</t>
-  </si>
-  <si>
     <t>Tope imponible del seguro de cesantía</t>
   </si>
   <si>
+    <t>AFP Uno</t>
+  </si>
+  <si>
     <t>Sistema de salud</t>
   </si>
   <si>
@@ -302,7 +320,7 @@
     <t>Tablas oficiales de Chile</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -329,9 +347,6 @@
     <t>Comisión mensual de cada AFP</t>
   </si>
   <si>
-    <t>AFP Capital</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
@@ -344,31 +359,16 @@
     <t>7/10/2026</t>
   </si>
   <si>
-    <t>AFP Cuprum</t>
-  </si>
-  <si>
-    <t>AFP Modelo</t>
-  </si>
-  <si>
-    <t>AFP PlanVital</t>
-  </si>
-  <si>
-    <t>AFP ProVida</t>
-  </si>
-  <si>
-    <t>AFP Uno</t>
-  </si>
-  <si>
     <t>Unidad de Fomento (UF)</t>
   </si>
   <si>
-    <t>Valor al 19/10/2026</t>
+    <t>Valor al 20/10/2026</t>
   </si>
   <si>
     <t>CLP</t>
   </si>
   <si>
-    <t>19/10/2026</t>
+    <t>20/10/2026</t>
   </si>
   <si>
     <t>https://www.sii.cl/valores_y_fechas/uf/uf2026.htm</t>
@@ -1188,7 +1188,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1197,82 +1197,106 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-    </row>
-    <row r="3" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="Z1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="5:26" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="Z3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="Z4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" s="8">
         <v>1200000</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B6" s="8">
         <v>0</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F6" s="12">
         <f>ROUND('Tablas oficiales'!$C$13*'Tablas oficiales'!$C$11,0)</f>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="Z6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F7" s="12">
         <f>ROUND('Tablas oficiales'!$C$14*'Tablas oficiales'!$C$11,0)</f>
       </c>
+      <c r="Z7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F8" s="12">
         <f>MIN(B5,F6)</f>
@@ -1280,16 +1304,16 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B9" s="14">
         <v>0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F9" s="15">
         <f>'Tablas oficiales'!$C$15+INDEX('Tablas oficiales'!$C$4:$C$10,MATCH(B7,'Tablas oficiales'!$B$4:$B$10,0))</f>
@@ -1297,13 +1321,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F10" s="12">
         <f>ROUND(F8*F9/100,0)</f>
@@ -1311,7 +1335,7 @@
     </row>
     <row r="11" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E11" s="11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F11" s="12">
         <f>ROUND(F8*'Tablas oficiales'!$C$16/100,0)</f>
@@ -1319,12 +1343,12 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F12" s="12">
         <f>IF(B8="Isapre",ROUND(B9*'Tablas oficiales'!$C$11,0),0)</f>
@@ -1332,13 +1356,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" s="17">
         <f>B5</f>
       </c>
       <c r="E13" s="11" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F13" s="12">
         <f>MAX(F11,F12)</f>
@@ -1346,13 +1370,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B14" s="17">
         <f>F10</f>
       </c>
       <c r="E14" s="11" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F14" s="12">
         <f>IF(B10="Indefinido",ROUND(MIN(B5,F7)*'Tablas oficiales'!$C$17/100,0),0)</f>
@@ -1360,7 +1384,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B15" s="17">
         <f>F13</f>
@@ -1368,24 +1392,24 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B16" s="17">
         <f>F14</f>
       </c>
       <c r="E16" s="10" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B17" s="17">
         <f>F17</f>
       </c>
       <c r="E17" s="11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F17" s="12">
         <f>MAX(0,B5-F10-F11-F14)</f>
@@ -1393,13 +1417,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B18" s="17">
         <f>F19</f>
       </c>
       <c r="E18" s="11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F18" s="18">
         <f>F17/'Tablas oficiales'!$C$12</f>
@@ -1407,13 +1431,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B19" s="17">
         <f>F20</f>
       </c>
       <c r="E19" s="11" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F19" s="12">
         <f>ROUND(IF(F18&lt;=0,0,INDEX('Tablas oficiales'!$E$20:$E$27,IFERROR(MATCH(F18,'Tablas oficiales'!$B$20:$B$27,1),1))+(F18-INDEX('Tablas oficiales'!$B$20:$B$27,IFERROR(MATCH(F18,'Tablas oficiales'!$B$20:$B$27,1),1)))*INDEX('Tablas oficiales'!$D$20:$D$27,IFERROR(MATCH(F18,'Tablas oficiales'!$B$20:$B$27,1),1))/100)*'Tablas oficiales'!$C$12,0)</f>
@@ -1421,13 +1445,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B20" s="17">
         <f>B6</f>
       </c>
       <c r="E20" s="11" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F20" s="12">
         <f>F10+F13+F14+F19</f>
@@ -1435,7 +1459,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B21" s="20">
         <f>B5-F20+B6</f>
@@ -1443,7 +1467,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B22" s="17">
         <f>F6</f>
@@ -1451,7 +1475,7 @@
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1472,8 +1496,8 @@
       <formula1>0</formula1>
       <formula2>1000000000000</formula2>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B7">
-      <formula1>'Tablas oficiales'!$B$4:$B$10</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Tu AFP)." sqref="B7">
+      <formula1>'Sueldo líquido'!$Z$1:$Z$7</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B8">
       <formula1>"Fonasa,Isapre"</formula1>
@@ -1506,25 +1530,25 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="11" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F4" s="12">
         <f>B5*'Tablas oficiales'!$C$30/100</f>
@@ -1532,16 +1556,16 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B5" s="8">
         <v>900000</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F5" s="12">
         <f>'Tablas oficiales'!$C$31*'Tablas oficiales'!$C$29/12</f>
@@ -1549,13 +1573,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B6" s="21">
         <v>12</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F6" s="12">
         <f>MIN(F4,F5)</f>
@@ -1563,14 +1587,14 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B9" s="17">
         <f>ROUND(F4,0)</f>
@@ -1578,7 +1602,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B10" s="17">
         <f>ROUND(F5,0)</f>
@@ -1586,7 +1610,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B11" s="20">
         <f>ROUND(F6,0)</f>
@@ -1594,7 +1618,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B12" s="17">
         <f>ROUND(F6*B6,0)</f>
@@ -1602,7 +1626,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B13" s="17">
         <f>'Tablas oficiales'!$C$29</f>
@@ -1610,7 +1634,7 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1656,44 +1680,44 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B5" s="22">
         <v>44635</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B6" s="22">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F6" s="23">
         <f>IF(EDATE(B5,12*(YEAR(B6)-YEAR(B5)))&gt;B6,(YEAR(B6)-YEAR(B5))-1,(YEAR(B6)-YEAR(B5)))</f>
@@ -1701,16 +1725,16 @@
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B7" s="8">
         <v>1200000</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F7" s="24">
         <f>EDATE(B5,12*F6)</f>
@@ -1718,13 +1742,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F8" s="23">
         <f>MIN(12,IF(EDATE(F7,((YEAR(B6)-YEAR(F7))*12+MONTH(B6)-MONTH(F7)))&gt;B6,((YEAR(B6)-YEAR(F7))*12+MONTH(B6)-MONTH(F7))-1,((YEAR(B6)-YEAR(F7))*12+MONTH(B6)-MONTH(F7))))</f>
@@ -1732,13 +1756,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F9" s="23">
         <f>B6-EDATE(F7,F8)</f>
@@ -1746,7 +1770,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B10" s="14">
         <v>0</v>
@@ -1754,18 +1778,18 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E12" s="11" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F12" s="12">
         <f>ROUND('Tablas oficiales'!$C$32*'Tablas oficiales'!$C$11,0)</f>
@@ -1773,12 +1797,12 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="E13" s="11" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F13" s="12">
         <f>MIN(B7,F12)</f>
@@ -1791,7 +1815,7 @@
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
       <c r="E14" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F14" s="23">
         <f>F6+IF(OR(F8&gt;6,AND(F8=6,F9&gt;0)),1,0)</f>
@@ -1799,13 +1823,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B15" s="26">
         <f>F6&amp;" años, "&amp;F8&amp;" meses y "&amp;F9&amp;" días"</f>
       </c>
       <c r="E15" s="11" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F15" s="23">
         <f>IF(AND(B8="Necesidades de la empresa (despido art. 161)",F6&gt;=1),IF(B5&lt;DATE(1981,8,14),F14*'Tablas oficiales'!$C$33,MIN(F14*'Tablas oficiales'!$C$33,'Tablas oficiales'!$C$34)),0)</f>
@@ -1813,13 +1837,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B16" s="17">
         <f>F13</f>
       </c>
       <c r="E16" s="11" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F16" s="12">
         <f>ROUND(F13*F15/30,0)</f>
@@ -1827,13 +1851,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B17" s="27">
         <f>IF(B8="Necesidades de la empresa (despido art. 161)",F14,0)</f>
       </c>
       <c r="E17" s="11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F17" s="12">
         <f>IF(AND(B8="Necesidades de la empresa (despido art. 161)",B9="No"),F13,0)</f>
@@ -1841,7 +1865,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B18" s="17">
         <f>F16</f>
@@ -1849,24 +1873,24 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B19" s="17">
         <f>F17</f>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B20" s="28">
         <f>F24</f>
       </c>
       <c r="E20" s="11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F20" s="23">
         <f>IF(B11="Sí",'Tablas oficiales'!$C$35,'Tablas oficiales'!$C$36)</f>
@@ -1874,13 +1898,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B21" s="17">
         <f>F25</f>
       </c>
       <c r="E21" s="11" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F21" s="18">
         <f>F20/12*F8+F20/12/30*F9+B10</f>
@@ -1888,13 +1912,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B22" s="20">
         <f>F16+F17+F25</f>
       </c>
       <c r="E22" s="11" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F22" s="23">
         <f>MAX(0,ROUNDUP(F21-0.000000001,0))</f>
@@ -1902,7 +1926,7 @@
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E23" s="11" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F23" s="23">
         <f>WORKDAY(B6,F22)-B6-F22</f>
@@ -1910,12 +1934,12 @@
     </row>
     <row r="24" ht="51" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="E24" s="11" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F24" s="18">
         <f>F21+F23</f>
@@ -1923,7 +1947,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="11" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F25" s="12">
         <f>ROUND(B7/30*F24,0)</f>
@@ -1984,7 +2008,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -1995,7 +2019,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2006,186 +2030,186 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F3" s="30" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="C4" s="32">
         <v>1.44</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="C5" s="35">
         <v>1.44</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C6" s="32">
         <v>1.27</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="C7" s="35">
         <v>0.58</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="31" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="C8" s="32">
         <v>1.16</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="C9" s="35">
         <v>1.45</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F9" s="36" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="31" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="C10" s="32">
         <v>0.46</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2196,7 +2220,7 @@
         <v>115</v>
       </c>
       <c r="C11" s="35">
-        <v>41183.94</v>
+        <v>41189.24</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>116</v>
@@ -2208,7 +2232,7 @@
         <v>118</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2225,13 +2249,13 @@
         <v>116</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F12" s="33" t="s">
         <v>121</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2254,7 +2278,7 @@
         <v>126</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2277,7 +2301,7 @@
         <v>126</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2291,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E15" s="34" t="s">
         <v>129</v>
@@ -2300,12 +2324,12 @@
         <v>130</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>123</v>
@@ -2314,7 +2338,7 @@
         <v>7</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E16" s="31" t="s">
         <v>129</v>
@@ -2323,7 +2347,7 @@
         <v>131</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2337,7 +2361,7 @@
         <v>0.6</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E17" s="34" t="s">
         <v>129</v>
@@ -2346,7 +2370,7 @@
         <v>133</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2365,7 +2389,7 @@
         <v>136</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
@@ -2514,7 +2538,7 @@
         <v>143</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2528,7 +2552,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E30" s="34" t="s">
         <v>129</v>
@@ -2537,7 +2561,7 @@
         <v>145</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2560,7 +2584,7 @@
         <v>145</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2583,7 +2607,7 @@
         <v>145</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2606,7 +2630,7 @@
         <v>145</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2629,7 +2653,7 @@
         <v>145</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2652,7 +2676,7 @@
         <v>145</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2675,7 +2699,7 @@
         <v>145</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito»: pones tus fechas, tu remuneración y el motivo del término, y te dice las indemnizaciones y las vacaciones pendientes y proporcionales.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -320,7 +320,7 @@
     <t>Tablas oficiales de Chile</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -362,13 +362,13 @@
     <t>Unidad de Fomento (UF)</t>
   </si>
   <si>
-    <t>Valor al 20/10/2026</t>
+    <t>Valor al 21/10/2026</t>
   </si>
   <si>
     <t>CLP</t>
   </si>
   <si>
-    <t>20/10/2026</t>
+    <t>21/10/2026</t>
   </si>
   <si>
     <t>https://www.sii.cl/valores_y_fechas/uf/uf2026.htm</t>
@@ -1714,7 +1714,7 @@
         <v>67</v>
       </c>
       <c r="B6" s="22">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>68</v>
@@ -2220,7 +2220,7 @@
         <v>115</v>
       </c>
       <c r="C11" s="35">
-        <v>41189.24</v>
+        <v>41194.55</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>116</v>

--- a/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/cl/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito»: pones tus fechas, tu remuneración y el motivo del término, y te dice las indemnizaciones y las vacaciones pendientes y proporcionales.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 22/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -320,7 +320,7 @@
     <t>Tablas oficiales de Chile</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 22/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -362,13 +362,13 @@
     <t>Unidad de Fomento (UF)</t>
   </si>
   <si>
-    <t>Valor al 21/10/2026</t>
+    <t>Valor al 22/10/2026</t>
   </si>
   <si>
     <t>CLP</t>
   </si>
   <si>
-    <t>21/10/2026</t>
+    <t>22/10/2026</t>
   </si>
   <si>
     <t>https://www.sii.cl/valores_y_fechas/uf/uf2026.htm</t>
@@ -1714,7 +1714,7 @@
         <v>67</v>
       </c>
       <c r="B6" s="22">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>68</v>
@@ -2220,7 +2220,7 @@
         <v>115</v>
       </c>
       <c r="C11" s="35">
-        <v>41194.55</v>
+        <v>41199.85</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>116</v>
